--- a/LC76_Library_Audit_WorkingPapers.xlsx
+++ b/LC76_Library_Audit_WorkingPapers.xlsx
@@ -674,7 +674,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:B64"/>
+  <dimension ref="A1:B65"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="46" customWidth="1" style="20" min="1" max="1"/>
@@ -695,7 +695,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="15" customHeight="1" s="21">
       <c r="B4" s="24" t="n"/>
     </row>
@@ -938,7 +937,6 @@
         </is>
       </c>
     </row>
-    <row r="29"/>
     <row r="30" ht="41.25" customHeight="1" s="21">
       <c r="A30" s="27" t="inlineStr">
         <is>
@@ -951,7 +949,6 @@
         </is>
       </c>
     </row>
-    <row r="31"/>
     <row r="32" ht="41.25" customHeight="1" s="21">
       <c r="A32" s="27" t="inlineStr">
         <is>
@@ -1345,6 +1342,18 @@
       <c r="B64" s="28" t="inlineStr">
         <is>
           <t>Expedition Readiness Programme (EX-1–EX-9) charter approved by owner 4 Jul 2026 (handover doc 'LC76 EX Programme Charter'). RS close-out executed this session: LC76_Library_Audit_2026-07.html updated to mark RS-1–RS-11 complete / F35 closed / owner gates G1–G4 all resolved (status boxes in the established audit style — Section 05 header + COMPLETE note-box, per-RS DONE pills, Owner-Gates ALL-RESOLVED box, footer). New EX_Register sheet appended (ID|Session|Scope|Status|Date|Evidence/Notes) seeding EX-1…EX-9 as PENDING; that sheet — not this Summary — is the running status register for the EX programme henceforth. State confirmed pre-close: all LX rows (LX-001…LX-014) Closed; sole remediation-open TA = TA-002 (weighbridge, owner-gated); advisory-standing TA-007–010 unchanged. Gates: workbook formula-occurrence baseline preserved at 11 (no formula cells touched); testzip()==None; styles cloned via copy.copy(). sw.js NO bump and index.html NO bump — neither the audit doc nor the working papers is precached/indexed (internal governance files). Deliverables: LC76_Library_Audit_2026-07.html, LC76_Library_Audit_WorkingPapers.xlsx. NB when built, EX profiles 007–010 and R37/R38/R39 require web research + new-file sw.js bumps per their specs; this close-out adds no library files.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="27" t="inlineStr">
+        <is>
+          <t>WORKING-PAPERS STATUS PASS — RA-1 / TA-002 CLOSED (24 SEP 2026)</t>
+        </is>
+      </c>
+      <c r="B65" s="28" t="inlineStr">
+        <is>
+          <t>OI-111 executed. The loaded weighbridge (done 10 Aug 2026, closed in the register as OI-1) is now shown as done here too: RA-1 CLOSED, TA-002 Closed. The rest of the RA rows were checked against the Open Items Register and brought into line (RA-4 ruled 24 Jul; RA-9 set fitted 17 Sep); every still-open row names its live register item. TA-038's blank status set to Closed. The F10 (weighbridge) item carried from Phase 1 (row 23) is therefore discharged. Detail: EX_Register row OI-111-WP-PASS.</t>
         </is>
       </c>
     </row>
@@ -6804,7 +6813,6 @@
         </is>
       </c>
     </row>
-    <row r="29"/>
     <row r="30">
       <c r="A30" s="20" t="inlineStr"/>
       <c r="B30" s="56" t="inlineStr">
@@ -12725,7 +12733,7 @@
       </c>
       <c r="H4" s="32" t="inlineStr">
         <is>
-          <t>Weighbridge (owner action) — pending</t>
+          <t>Weighbridge (owner action) — pending || 24 Sep 2026 (working-papers pass, OI-111): DONE — loaded per-axle weighbridge 10 Aug 2026 (E1 slip; Facts §1).</t>
         </is>
       </c>
       <c r="I4" s="32" t="inlineStr">
@@ -12735,17 +12743,17 @@
       </c>
       <c r="J4" s="34" t="inlineStr">
         <is>
-          <t>Unreconciled (=audit F10)</t>
+          <t>Unreconciled (=audit F10) || 24 Sep 2026 (working-papers pass, OI-111): Loaded weight MEASURED; the kerb/payload split stays an estimate (a loaded pass cannot isolate unladen weight) and is no longer blocking; the 280 kg overload is owner decision OI-103.</t>
         </is>
       </c>
       <c r="K4" s="32" t="inlineStr">
         <is>
-          <t>Weighbridge loaded vehicle (per-axle+GCM); reconcile to one figure; propagate; flag provisional meanwhile</t>
+          <t>Weighbridge loaded vehicle (per-axle+GCM); reconcile to one figure; propagate; flag provisional meanwhile || 24 Sep 2026 (working-papers pass, OI-111): CLOSED with RA-1 (OI-1 closed 15 Sep 2026).</t>
         </is>
       </c>
       <c r="L4" s="32" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
@@ -14976,7 +14984,12 @@
       </c>
       <c r="K40" s="20" t="inlineStr">
         <is>
-          <t>RS-1 session, 3 Jul 2026: G2 RESOLVED by owner — jack/axle-stand minimum revised to &gt;=2.5 t rated equipment, with provisional-kerb caveat (~2,299 kg, weighbridge pending TA-002). Execution scheduled in RS-3 (R27 dedicated session, 130 KB). Status remains Open until R27 edit lands. || RS-3 session, 3 Jul 2026: EXECUTED — R27 checklist item 12 revised to '&gt;=2.5 t, inspected' with provisional-kerb caveat (~2,299 kg, weighbridge pending). TA-038 CLOSED.</t>
+          <t>RS-1 session, 3 Jul 2026: G2 RESOLVED by owner — jack/axle-stand minimum revised to &gt;=2.5 t rated equipment, with provisional-kerb caveat (~2,299 kg, weighbridge pending TA-002). Execution scheduled in RS-3 (R27 dedicated session, 130 KB). Status remains Open until R27 edit lands. || RS-3 session, 3 Jul 2026: EXECUTED — R27 checklist item 12 revised to '&gt;=2.5 t, inspected' with provisional-kerb caveat (~2,299 kg, weighbridge pending). TA-038 CLOSED. || 24 Sep 2026 (working-papers pass, OI-111): Status cell was blank; set to Closed to match the verdict (hygiene only; noted on OI-65).</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>Closed</t>
         </is>
       </c>
     </row>
@@ -16173,7 +16186,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F40"/>
+  <dimension ref="A1:F41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" style="21" min="1" max="1"/>
@@ -16468,7 +16481,7 @@
       </c>
       <c r="F9" s="32" t="inlineStr">
         <is>
-          <t>Largest cross-file session — consider split EX-8a (R3+R23) / EX-8b (retrofit) under context pressure. R3/R23 + retrofit are content-only edits to existing precached files -&gt; NO sw.js bump. Supplier-naming discipline. Opus. | 9 Jul 2026: projected expedition distance corrected 40,000 -&gt; 60,000+ km (owner decision, Gate 2) — ledger quantities scale accordingly. En-route service policy: Toyota dealers where route allows; oil changes never deferred (also RA-2 sampling points).</t>
+          <t>Largest cross-file session — consider split EX-8a (R3+R23) / EX-8b (retrofit) under context pressure. R3/R23 + retrofit are content-only edits to existing precached files -&gt; NO sw.js bump. Supplier-naming discipline. Opus. | 9 Jul 2026: projected expedition distance corrected 40,000 -&gt; 60,000+ km (owner decision, Gate 2) — ledger quantities scale accordingly. En-route service policy: Toyota dealers where route allows; oil changes never deferred (also RA-2 sampling points). || 24 Sep 2026 (working-papers pass, OI-111): Checked against the Open Items Register (master of status): still open. Live status is kept on OI-11, not here.</t>
         </is>
       </c>
     </row>
@@ -16500,7 +16513,7 @@
       </c>
       <c r="F10" s="32" t="inlineStr">
         <is>
-          <t>Output: decisions minuted -&gt; R38 §3 update (content-only, no sw.js). Possible second itinerary doc (new file -&gt; sw.js bump) if owner wants the route formalised like the Karoo doc. Interactive (not a rote build).</t>
+          <t>Output: decisions minuted -&gt; R38 §3 update (content-only, no sw.js). Possible second itinerary doc (new file -&gt; sw.js bump) if owner wants the route formalised like the Karoo doc. Interactive (not a rote build). || 24 Sep 2026 (working-papers pass, OI-111): Checked against the Open Items Register (master of status): still open. Live status is kept on OI-12, not here.</t>
         </is>
       </c>
     </row>
@@ -16532,7 +16545,7 @@
       </c>
       <c r="F11" s="32" t="inlineStr">
         <is>
-          <t>Chartered 8 Jul 2026 from external consultant strategic review. Trigger-dated: schedule ~6 months before expedition departure. Content-only expected; masthead date bumps per standard.</t>
+          <t>Chartered 8 Jul 2026 from external consultant strategic review. Trigger-dated: schedule ~6 months before expedition departure. Content-only expected; masthead date bumps per standard. || 24 Sep 2026 (working-papers pass, OI-111): Checked against the Open Items Register (master of status): still open. Live status is kept on OI-14, not here.</t>
         </is>
       </c>
     </row>
@@ -16564,7 +16577,7 @@
       </c>
       <c r="F12" s="32" t="inlineStr">
         <is>
-          <t>Chartered 8 Jul 2026 (consultant review). Uses DG Section 16 print standard. Claude produces pack; physical print/laminate is owner action.</t>
+          <t>Chartered 8 Jul 2026 (consultant review). Uses DG Section 16 print standard. Claude produces pack; physical print/laminate is owner action. || 24 Sep 2026 (working-papers pass, OI-111): Checked against the Open Items Register (master of status): still open. Live status is kept on OI-10, not here.</t>
         </is>
       </c>
     </row>
@@ -16586,17 +16599,17 @@
       </c>
       <c r="D13" s="32" t="inlineStr">
         <is>
-          <t>OPEN — owner-gated</t>
+          <t>CLOSED — weighed 10 Aug 2026 (OI-1 closed 15 Sep 2026)</t>
         </is>
       </c>
       <c r="E13" s="32" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>10 Aug 2026</t>
         </is>
       </c>
       <c r="F13" s="32" t="inlineStr">
         <is>
-          <t>Same physical action as TA-002 (weighbridge), deadline sharpened to pre-Karoo, 8 Jul 2026. Closing RA-1 closes TA-002. | 9 Jul 2026 (logistics assessment): THREE kerb/payload pairs now confirmed circulating — ~2,160/~690, ~2,299/~551 (R12/Facts), ~2,287/~563 (R11 component table). All tagged RA-1-gated provisional (R11 M5); closure = single library-wide propagation from weighbridge slip (R11, R12, Facts §2). Insurance-validity dimension added to R29 §2/§11 (M1/M2). | 9 Jul 2026 (Toyota confirmation): factory kerb 2,190 kg and GVM 3,000 kg CONFIRMED by Toyota (supersedes 2,850 kg GVM and all three provisional kerb pairs). Library-wide propagation executed same session (17 files: Facts §2, R11 §2 full re-baseline, R1, R9, R12, R14, R19, R21, R25, R27, R28, R29, R30, index, Trip Fuel Planner, Fuel Range Calc, Tyre Pressure Calc). As-built kerb ~2,317 kg and payload ~683 kg remain ESTIMATES (accessory net +127 kg per R11). RA-1 SCOPE NARROWED: weighbridge now verifies as-built kerb + loaded weight vs 3,000 kg GVM only — factory figures no longer part of the uncertainty. Deadline unchanged: full Karoo trim, before 3 Aug.</t>
+          <t>Same physical action as TA-002 (weighbridge), deadline sharpened to pre-Karoo, 8 Jul 2026. Closing RA-1 closes TA-002. | 9 Jul 2026 (logistics assessment): THREE kerb/payload pairs now confirmed circulating — ~2,160/~690, ~2,299/~551 (R12/Facts), ~2,287/~563 (R11 component table). All tagged RA-1-gated provisional (R11 M5); closure = single library-wide propagation from weighbridge slip (R11, R12, Facts §2). Insurance-validity dimension added to R29 §2/§11 (M1/M2). | 9 Jul 2026 (Toyota confirmation): factory kerb 2,190 kg and GVM 3,000 kg CONFIRMED by Toyota (supersedes 2,850 kg GVM and all three provisional kerb pairs). Library-wide propagation executed same session (17 files: Facts §2, R11 §2 full re-baseline, R1, R9, R12, R14, R19, R21, R25, R27, R28, R29, R30, index, Trip Fuel Planner, Fuel Range Calc, Tyre Pressure Calc). As-built kerb ~2,317 kg and payload ~683 kg remain ESTIMATES (accessory net +127 kg per R11). RA-1 SCOPE NARROWED: weighbridge now verifies as-built kerb + loaded weight vs 3,000 kg GVM only — factory figures no longer part of the uncertainty. Deadline unchanged: full Karoo trim, before 3 Aug. || 24 Sep 2026 (working-papers pass, OI-111): CLOSED. Loaded per-axle weighbridge done 10 Aug 2026 in full expedition trim (full fuel, 60 L water, all gear): front 1,160 kg, rear 2,120 kg, gross 3,280 kg (E1, weighbridge slip; Facts §1). Legal on each axle (rear the binding axle, 60 kg under its 2,180 kg maximum) but 280 kg OVER the 3,000 kg GVM. Recorded and closed in the Open Items Register 15 Sep 2026 as OI-1. The as-built kerb/payload split is NOT resolved — a loaded pass does not isolate unladen weight — so those stay estimates, no longer blocking. The overload is now an owner decision (OI-103). Closes TA-002 (same physical action).</t>
         </is>
       </c>
     </row>
@@ -16628,7 +16641,7 @@
       </c>
       <c r="F14" s="32" t="inlineStr">
         <is>
-          <t>Chartered 8 Jul 2026. Ideally baseline before Karoo loop. Results feed R8/Facts; oil-analysis cadence joins the service routine.</t>
+          <t>Chartered 8 Jul 2026. Ideally baseline before Karoo loop. Results feed R8/Facts; oil-analysis cadence joins the service routine. || 24 Sep 2026 (working-papers pass, OI-111): Checked against the Open Items Register (master of status): still open. Live status is kept on OI-5, not here.</t>
         </is>
       </c>
     </row>
@@ -16660,7 +16673,7 @@
       </c>
       <c r="F15" s="32" t="inlineStr">
         <is>
-          <t>Chartered 8 Jul 2026. Schedule alongside a pre-departure service at a diesel workshop. | 9 Jul 2026: Gate 1 decision A CONFIRMED — belt is Apr 2025 @ 273,023 km (full kit incl. tensioner/idler/cover, per R23); pre-departure replacement ~T-3 months stands; removed belt becomes carried spare. R23 reconciled (S1/S2/S6 + triage row).</t>
+          <t>Chartered 8 Jul 2026. Schedule alongside a pre-departure service at a diesel workshop. | 9 Jul 2026: Gate 1 decision A CONFIRMED — belt is Apr 2025 @ 273,023 km (full kit incl. tensioner/idler/cover, per R23); pre-departure replacement ~T-3 months stands; removed belt becomes carried spare. R23 reconciled (S1/S2/S6 + triage row). || 24 Sep 2026 (working-papers pass, OI-111): Checked against the Open Items Register (master of status): still open. Live status is kept on OI-21, not here.</t>
         </is>
       </c>
     </row>
@@ -16682,17 +16695,17 @@
       </c>
       <c r="D16" s="32" t="inlineStr">
         <is>
-          <t>OPEN — owner-gated</t>
+          <t>RULED 24 Jul 2026 — no spare alternator; kit purchase open (OI-68), jump-pack recharge open (OI-46)</t>
         </is>
       </c>
       <c r="E16" s="32" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>24 Jul 2026</t>
         </is>
       </c>
       <c r="F16" s="32" t="inlineStr">
         <is>
-          <t>Chartered 8 Jul 2026. Feeds R3 Expedition Consumables Ledger (EX-8) spares schedule.</t>
+          <t>Chartered 8 Jul 2026. Feeds R3 Expedition Consumables Ledger (EX-8) spares schedule. || 24 Sep 2026 (working-papers pass, OI-111): Status brought into line with the Open Items Register. The owner ruled 24 Jul 2026 (see row RA-4-RULING; OI-45 closed): no complete spare alternator; carry a brush/regulator kit, starter kit and spare V-belts. Still open from the ruling: buying that kit (OI-68) and confirming how the jump pack is recharged in the field (OI-46).</t>
         </is>
       </c>
     </row>
@@ -16724,7 +16737,7 @@
       </c>
       <c r="F17" s="32" t="inlineStr">
         <is>
-          <t>Chartered 8 Jul 2026. R22 covers theory; this is the hardware-age action.</t>
+          <t>Chartered 8 Jul 2026. R22 covers theory; this is the hardware-age action. || 24 Sep 2026 (working-papers pass, OI-111): Checked against the Open Items Register (master of status): still open. Live status is kept on OI-6, not here.</t>
         </is>
       </c>
     </row>
@@ -16756,7 +16769,7 @@
       </c>
       <c r="F18" s="32" t="inlineStr">
         <is>
-          <t>Chartered 8 Jul 2026. Highest-consequence readiness item. Completion recorded in R37 training register.</t>
+          <t>Chartered 8 Jul 2026. Highest-consequence readiness item. Completion recorded in R37 training register. || 24 Sep 2026 (working-papers pass, OI-111): Checked against the Open Items Register (master of status): still open. Live status is kept on OI-4, not here.</t>
         </is>
       </c>
     </row>
@@ -16788,7 +16801,7 @@
       </c>
       <c r="F19" s="32" t="inlineStr">
         <is>
-          <t>Chartered 8 Jul 2026. Outcomes recorded in R37. | 9 Jul 2026: pinned in R37 §7 calendar (before 3 Aug 2026).</t>
+          <t>Chartered 8 Jul 2026. Outcomes recorded in R37. | 9 Jul 2026: pinned in R37 §7 calendar (before 3 Aug 2026). || 24 Sep 2026 (working-papers pass, OI-111): Checked against the Open Items Register (master of status): still open. Live status is kept on OI-2, not here.</t>
         </is>
       </c>
     </row>
@@ -16820,7 +16833,7 @@
       </c>
       <c r="F20" s="32" t="inlineStr">
         <is>
-          <t>Chartered 8 Jul 2026. Feeds R37 (skills) and R38 (crew redundancy). Assess on Karoo return via R23 post-trip review. | 9 Jul 2026: scenario row + calendar row added to R37; pass standard defined (solo recovery, solo dirt leg, solo comms tree).</t>
+          <t>Chartered 8 Jul 2026. Feeds R37 (skills) and R38 (crew redundancy). Assess on Karoo return via R23 post-trip review. | 9 Jul 2026: scenario row + calendar row added to R37; pass standard defined (solo recovery, solo dirt leg, solo comms tree). || 24 Sep 2026 (working-papers pass, OI-111): Checked against the Open Items Register (master of status): still open. Live status is kept on OI-72, not here.</t>
         </is>
       </c>
     </row>
@@ -16842,17 +16855,17 @@
       </c>
       <c r="D21" s="32" t="inlineStr">
         <is>
-          <t>OPEN — owner decision</t>
+          <t>SET FITTED 17 Sep 2026 — proving under way (OI-22); second spare open (OI-19)</t>
         </is>
       </c>
       <c r="E21" s="32" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>17 Sep 2026</t>
         </is>
       </c>
       <c r="F21" s="32" t="inlineStr">
         <is>
-          <t>Chartered 8 Jul 2026. Decision feeds R14/R19 and Facts on execution; pressure tables re-derived after RA-1 weighbridge.</t>
+          <t>Chartered 8 Jul 2026. Decision feeds R14/R19 and Facts on execution; pressure tables re-derived after RA-1 weighbridge. || 24 Sep 2026 (working-papers pass, OI-111): Status brought into line with the Open Items Register. BFG All-Terrain KO3 265/75R16 load range D fitted 17 Sep 2026 (4 + matching spare; Facts §6), pulled forward by a third Maxxis sidewall failure; the ≥5,000 km proving run is under way (OI-22). The second-spare / casing-repair strategy for East Africa is still open (OI-19). Tyre-choice criteria now recorded in LC76_Programmes_Reference.txt (RA-9).</t>
         </is>
       </c>
     </row>
@@ -16884,7 +16897,7 @@
       </c>
       <c r="F22" s="32" t="inlineStr">
         <is>
-          <t>Chartered 8 Jul 2026. If hardware absent, procurement joins R3 ledger (EX-8). | 9 Jul 2026: fail-safe layer block added to R38 §1 (device/registration/live-test/named-owner placeholders). | 11 Jul 2026 (R29 evaluation, change map M1–M5 executed): RA-10 scope EXTENDED to the satellite voice phone. Owner resolution: satphone NOT owned — planned pre-departure purchase; doctrine = inReach Mini 2 (owned, tracking/GPS/SOS) + sat phone (emergency voice). R16 §6 verification block extended items 6–9 (Garmin IERCC portal registration + mandatory handset Assistance Button config / SIM &amp; airtime live / scheduled IERCC SOS test / carried accessibly); R38 §1 sign-off rows 4–5 added (contingent until purchase); Facts §11C device inventory added; R29 §7/§11 reframed to planned status; R10 §9 activation drill synced. GEOS registration path DEAD (Garmin acquisition) — all library references migrated to the Garmin IERCC Registration Portal. Physical verification (inReach live test pre-Karoo; satphone regime from purchase) remains the open owner action — status stays OPEN.</t>
+          <t>Chartered 8 Jul 2026. If hardware absent, procurement joins R3 ledger (EX-8). | 9 Jul 2026: fail-safe layer block added to R38 §1 (device/registration/live-test/named-owner placeholders). | 11 Jul 2026 (R29 evaluation, change map M1–M5 executed): RA-10 scope EXTENDED to the satellite voice phone. Owner resolution: satphone NOT owned — planned pre-departure purchase; doctrine = inReach Mini 2 (owned, tracking/GPS/SOS) + sat phone (emergency voice). R16 §6 verification block extended items 6–9 (Garmin IERCC portal registration + mandatory handset Assistance Button config / SIM &amp; airtime live / scheduled IERCC SOS test / carried accessibly); R38 §1 sign-off rows 4–5 added (contingent until purchase); Facts §11C device inventory added; R29 §7/§11 reframed to planned status; R10 §9 activation drill synced. GEOS registration path DEAD (Garmin acquisition) — all library references migrated to the Garmin IERCC Registration Portal. Physical verification (inReach live test pre-Karoo; satphone regime from purchase) remains the open owner action — status stays OPEN. || 24 Sep 2026 (working-papers pass, OI-111): Checked against the Open Items Register (master of status): still open. Live status is kept on OI-3, not here.</t>
         </is>
       </c>
     </row>
@@ -17432,7 +17445,7 @@
         </is>
       </c>
     </row>
-    <row r="40">
+    <row r="40" s="21">
       <c r="A40" s="32" t="inlineStr">
         <is>
           <t>RA-4-RULING</t>
@@ -17461,6 +17474,38 @@
       <c r="F40" s="32" t="inlineStr">
         <is>
           <t>OWNER RULING 24 Jul 2026: no complete spare alternator carried. Rationale recorded — 70-Series alternator is a commonly available part on the route, the unit is heavy and expensive, payload PROVISIONAL until RA-1. Carried redundancy: brush/regulator kit + starter contact/solenoid kit + spare V-belt set; replacement sourced en route. Executed at pinned HEAD 965b0962, owner document first. R32 (owns crank-battery doctrine) gained an expedition-consequence rule box: the alternator is the crank battery's ONLY charge source (solar and shore power serve the house bank, Orion is one-way, starting off the LiFePO4 is prohibited), so on alternator failure every charging path into the Willard fails and the ARB jump pack becomes the sole path to a start. R41 C1 chain-breaker rewritten from 'swap the unit' to 'detect early, limp somewhere recoverable, source en route'; R32 §8 checks (especially AC ripple for a failing diode pack) promoted to load-bearing; noted that the kit does NOT fix a diode pack. R31 CORRECTED — its claim that 'the refurbished stock unit also serves as the field spare' was a leftover from the REJECTED high-output alternator case; no displaced unit ever existed, so the library had asserted a spare that does not exist, in one document, propagated nowhere. R3 gained item 4.7 Alternator Brush &amp; Regulator Kit (belts 1.3 and starter solenoid 4.6 already carried). DEFECT FOUND AND FIXED IN THE SAME PASS: R41 C1 carried 'Emergency bridge: the house bank can jump the crank side in extremis', directly contradicting R32's explicit prohibition on starting off the LiFePO4. A cross-document contradiction on a life-of-the-vehicle procedure. Removed; R41 now points at R32 as owner. PROCESS DEFECT DISCLOSED: an edit script re-run after two partial anchor failures applied the R32 insertion TWICE (the anchor survived inside its own replacement, so the guard could not catch it). Detected by a post-edit count, R32 restored from the pinned SHA and re-applied once. LESSON: assert count==1 protects the anchor, not idempotence — a script that may be re-run must also assert the NEW content is absent before writing. VALIDATION: depth walks 0/0/0 across eleven tag types on R32, R41, R31, R3 and R30; ids unique; TOC targets resolve; node --check clean. ROLL-FORWARD on the OIR: declared -OI-45 +OI-46 +1 log entry; actual matched exactly, reconciled. PROPAGATION: R30 +3 topic rows; OIR header, OI-45 closed, OI-46 opened; mastheads R32/R41/R31/R3 24 Jul. Content-only — CACHE stays v24. Next free open item OI-47. Opus.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="32" t="inlineStr">
+        <is>
+          <t>OI-111-WP-PASS</t>
+        </is>
+      </c>
+      <c r="B41" s="32" t="inlineStr">
+        <is>
+          <t>Working-papers status pass — RA-1 / TA-002 flip + RA reconciliation</t>
+        </is>
+      </c>
+      <c r="C41" s="32" t="inlineStr">
+        <is>
+          <t>Close RA-1 and TA-002 (loaded weighbridge done 10 Aug 2026), and bring every RA/EX row's status into line with the Open Items Register, which is master of status.</t>
+        </is>
+      </c>
+      <c r="D41" s="32" t="inlineStr">
+        <is>
+          <t>CLOSED — OI-111 closed</t>
+        </is>
+      </c>
+      <c r="E41" s="32" t="inlineStr">
+        <is>
+          <t>24 Sep 2026</t>
+        </is>
+      </c>
+      <c r="F41" s="32" t="inlineStr">
+        <is>
+          <t>Executed 24 Sep 2026 at HEAD 24b704d4 (live file fetched SHA-pinned; identical to main). RA-1 -&gt; CLOSED (weighed 10 Aug 2026; OI-1). RA-4 -&gt; RULED 24 Jul 2026 with OI-68/OI-46 open. RA-9 -&gt; SET FITTED 17 Sep 2026, proving (OI-22), second spare open (OI-19). RA-2/3/5/6/7/8/10 and EX-8..11 confirmed still open; each row now names its live register item. TA_Register: TA-002 -&gt; Closed; TA-038 blank status -&gt; Closed to match its verdict. Append-only: no existing text removed. COUNTIF formula-cell baseline 9 preserved; recalc.py not run (the workbook recalculates on open); testzip None.</t>
         </is>
       </c>
     </row>

--- a/LC76_Library_Audit_WorkingPapers.xlsx
+++ b/LC76_Library_Audit_WorkingPapers.xlsx
@@ -674,7 +674,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:B65"/>
+  <dimension ref="A1:B66"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="46" customWidth="1" style="20" min="1" max="1"/>
@@ -826,7 +826,7 @@
         </is>
       </c>
       <c r="B17" s="24">
-        <f>COUNTIFS(TA_Register!L:L,"Open")</f>
+        <f>COUNTIF(TA_Register!L:L,"Open*")</f>
         <v/>
       </c>
     </row>
@@ -837,7 +837,7 @@
         </is>
       </c>
       <c r="B18" s="24">
-        <f>COUNTIFS(TA_Register!F:F,"HIGH")+COUNTIFS(TA_Register!F:F,"S")</f>
+        <f>COUNTIFS(TA_Register!L:L,"Open*",TA_Register!F:F,"HIGH")+COUNTIFS(TA_Register!L:L,"Open*",TA_Register!F:F,"S")</f>
         <v/>
       </c>
     </row>
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="B19" s="24">
-        <f>COUNTIF(TA_Register!L:L,"Closed")</f>
+        <f>COUNTIF(TA_Register!L:L,"Closed*")</f>
         <v/>
       </c>
     </row>
@@ -859,7 +859,7 @@
         </is>
       </c>
       <c r="B20" s="24">
-        <f>COUNTIF(LX_Register!H:H,"Open")</f>
+        <f>COUNTIF(LX_Register!H:H,"Open*")</f>
         <v/>
       </c>
     </row>
@@ -1354,6 +1354,18 @@
       <c r="B65" s="28" t="inlineStr">
         <is>
           <t>OI-111 executed. The loaded weighbridge (done 10 Aug 2026, closed in the register as OI-1) is now shown as done here too: RA-1 CLOSED, TA-002 Closed. The rest of the RA rows were checked against the Open Items Register and brought into line (RA-4 ruled 24 Jul; RA-9 set fitted 17 Sep); every still-open row names its live register item. TA-038's blank status set to Closed. The F10 (weighbridge) item carried from Phase 1 (row 23) is therefore discharged. Detail: EX_Register row OI-111-WP-PASS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="27" t="inlineStr">
+        <is>
+          <t>SUMMARY COUNTS CORRECTED (24 SEP 2026, owner-approved)</t>
+        </is>
+      </c>
+      <c r="B66" s="28" t="inlineStr">
+        <is>
+          <t>Four FINDINGS formulas counted only an exact status word, so they missed 'Open (advisory)', 'OPEN — OI-60' and 'Closed (§5)', and the High/safety line counted every finding ever raised, open or closed. Now: B17 and B20 count any status starting 'Open' (COUNTIF wildcards ignore case); B19 counts any status starting 'Closed'; B18 counts High/safety findings that are still OPEN, as its 'of which' label says. Expected on recalculation: TA open 4 (all advisory), of which High/safety 0, TA closed 35, LX open 1 (LX-016, OI-60). Formula-cell baseline stays 9 (same nine cells, still COUNTIF/COUNTIFS). Old formulas: B17 =COUNTIFS(TA_Register!L:L,"Open"); B18 =COUNTIFS(TA_Register!F:F,"HIGH")+COUNTIFS(TA_Register!F:F,"S"); B19 =COUNTIF(TA_Register!L:L,"Closed"); B20 =COUNTIF(LX_Register!H:H,"Open").</t>
         </is>
       </c>
     </row>
@@ -14987,7 +14999,7 @@
           <t>RS-1 session, 3 Jul 2026: G2 RESOLVED by owner — jack/axle-stand minimum revised to &gt;=2.5 t rated equipment, with provisional-kerb caveat (~2,299 kg, weighbridge pending TA-002). Execution scheduled in RS-3 (R27 dedicated session, 130 KB). Status remains Open until R27 edit lands. || RS-3 session, 3 Jul 2026: EXECUTED — R27 checklist item 12 revised to '&gt;=2.5 t, inspected' with provisional-kerb caveat (~2,299 kg, weighbridge pending). TA-038 CLOSED. || 24 Sep 2026 (working-papers pass, OI-111): Status cell was blank; set to Closed to match the verdict (hygiene only; noted on OI-65).</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr">
+      <c r="L40" s="20" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
